--- a/dist/config/config.xlsx
+++ b/dist/config/config.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowHeight="17655" activeTab="1"/>
+    <workbookView windowWidth="25600" windowHeight="10460" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="全局配置" sheetId="1" r:id="rId1"/>
@@ -1432,7 +1432,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2148" uniqueCount="501">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2189" uniqueCount="515">
   <si>
     <t>键</t>
   </si>
@@ -1692,30 +1692,57 @@
     <t>绿色</t>
   </si>
   <si>
+    <t>TEST</t>
+  </si>
+  <si>
+    <t>识别结果</t>
+  </si>
+  <si>
+    <t>会计月计表</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>C:\Users\AZI\Desktop\VibeCode\10.ScanToExcel\core\data\exports\OUTPUT.XLSX</t>
+  </si>
+  <si>
+    <t>HUIZONG</t>
+  </si>
+  <si>
     <t>Y</t>
   </si>
   <si>
-    <t>TEST</t>
-  </si>
-  <si>
-    <t>识别结果</t>
-  </si>
-  <si>
-    <t>会计月计表</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>C:\Users\AZI\Desktop\VibeCode\10.ScanToExcel\core\data\exports\OUTPUT.XLSX</t>
-  </si>
-  <si>
-    <t>HUIZONG</t>
-  </si>
-  <si>
     <t>A;B;C;D;E;F;G;H;I;J;K</t>
   </si>
   <si>
+    <t>汇总</t>
+  </si>
+  <si>
+    <t>两项净收入</t>
+  </si>
+  <si>
+    <t>表1</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>C:\Users\Azi\Desktop\156.2026年四季度两项净收入变动分析情况 (2)\156.2026年四季度两项净收入变动分析情况\156.2026年四季度两项净收入变动分析情况1\out.xlsx</t>
+  </si>
+  <si>
+    <t>分析表</t>
+  </si>
+  <si>
+    <t>A;B;C;D;E;F</t>
+  </si>
+  <si>
+    <t>汇总2</t>
+  </si>
+  <si>
+    <t>预测表</t>
+  </si>
+  <si>
     <t>映射名称</t>
   </si>
   <si>
@@ -2436,36 +2463,42 @@
     <t>报表名称</t>
   </si>
   <si>
+    <t>两项净收入分析情况</t>
+  </si>
+  <si>
+    <t>仲恺区存贷统计月报</t>
+  </si>
+  <si>
+    <t xml:space="preserve">人民币 </t>
+  </si>
+  <si>
+    <t>1人民币</t>
+  </si>
+  <si>
+    <t>sheet1@A1;sheet2@A2</t>
+  </si>
+  <si>
+    <t>示例：按文件内容单元格生成前缀</t>
+  </si>
+  <si>
+    <t>华润</t>
+  </si>
+  <si>
+    <t>珠海华润银行</t>
+  </si>
+  <si>
+    <t>5k03</t>
+  </si>
+  <si>
+    <t>数据日期</t>
+  </si>
+  <si>
+    <t>2026.09.</t>
+  </si>
+  <si>
     <t>仲恺区专项统计季报</t>
   </si>
   <si>
-    <t>仲恺区存贷统计月报</t>
-  </si>
-  <si>
-    <t xml:space="preserve">人民币 </t>
-  </si>
-  <si>
-    <t>1人民币</t>
-  </si>
-  <si>
-    <t>sheet1@A1;sheet2@A2</t>
-  </si>
-  <si>
-    <t>示例：按文件内容单元格生成前缀</t>
-  </si>
-  <si>
-    <t>华润</t>
-  </si>
-  <si>
-    <t>珠海华润银行</t>
-  </si>
-  <si>
-    <t>5k03</t>
-  </si>
-  <si>
-    <t>数据日期</t>
-  </si>
-  <si>
     <t xml:space="preserve">外币 </t>
   </si>
   <si>
@@ -2667,6 +2700,21 @@
     <t>澳门国际银行</t>
   </si>
   <si>
+    <t>占位符</t>
+  </si>
+  <si>
+    <t>华夏银行</t>
+  </si>
+  <si>
+    <t>农业发展银行</t>
+  </si>
+  <si>
+    <t>浙商银行</t>
+  </si>
+  <si>
+    <t>广东华润银行</t>
+  </si>
+  <si>
     <t>惠东农商</t>
   </si>
   <si>
@@ -2679,9 +2727,6 @@
     <t>惠东惠民</t>
   </si>
   <si>
-    <t>惠东惠民存在银行</t>
-  </si>
-  <si>
     <t>博罗长江</t>
   </si>
   <si>
@@ -2691,9 +2736,6 @@
     <t>建设银行</t>
   </si>
   <si>
-    <t>广东华润银行</t>
-  </si>
-  <si>
     <t>汇丰</t>
   </si>
   <si>
@@ -2703,61 +2745,61 @@
     <t>澳门</t>
   </si>
   <si>
+    <t>华润银行</t>
+  </si>
+  <si>
+    <t>华夏</t>
+  </si>
+  <si>
+    <t>农发行</t>
+  </si>
+  <si>
+    <t>原始机构名称</t>
+  </si>
+  <si>
+    <t>映射后机构名称</t>
+  </si>
+  <si>
+    <t>是否为外资行</t>
+  </si>
+  <si>
+    <t>中国农业发展银行</t>
+  </si>
+  <si>
+    <t>珠海华润银行股份有限公司</t>
+  </si>
+  <si>
+    <t>广东南粤银行股份有限公司</t>
+  </si>
+  <si>
+    <t>东莞农村商业银行有限公司</t>
+  </si>
+  <si>
+    <t>广东惠州农商行</t>
+  </si>
+  <si>
+    <t>广东龙门农村商业银行股份有限公司</t>
+  </si>
+  <si>
+    <t xml:space="preserve">香港汇丰银行                            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">香港东亚银行                            </t>
+  </si>
+  <si>
+    <t>澳门国际银行股份有限公司广州分行</t>
+  </si>
+  <si>
+    <t xml:space="preserve">广州市商业银行                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">东莞市商业银行                          </t>
+  </si>
+  <si>
+    <t>村镇银行</t>
+  </si>
+  <si>
     <t>广东华润银行股份有限公司</t>
-  </si>
-  <si>
-    <t>原始机构名称</t>
-  </si>
-  <si>
-    <t>映射后机构名称</t>
-  </si>
-  <si>
-    <t>是否为外资行</t>
-  </si>
-  <si>
-    <t>中国农业发展银行</t>
-  </si>
-  <si>
-    <t>华夏银行</t>
-  </si>
-  <si>
-    <t>浙商银行</t>
-  </si>
-  <si>
-    <t>珠海华润银行股份有限公司</t>
-  </si>
-  <si>
-    <t>广东南粤银行股份有限公司</t>
-  </si>
-  <si>
-    <t>东莞农村商业银行有限公司</t>
-  </si>
-  <si>
-    <t>广东惠州农商行</t>
-  </si>
-  <si>
-    <t>广东龙门农村商业银行股份有限公司</t>
-  </si>
-  <si>
-    <t xml:space="preserve">香港汇丰银行                            </t>
-  </si>
-  <si>
-    <t xml:space="preserve">香港东亚银行                            </t>
-  </si>
-  <si>
-    <t>澳门国际银行股份有限公司广州分行</t>
-  </si>
-  <si>
-    <t xml:space="preserve">广州市商业银行                          </t>
-  </si>
-  <si>
-    <t xml:space="preserve">东莞市商业银行                          </t>
-  </si>
-  <si>
-    <t>农业发展银行</t>
-  </si>
-  <si>
-    <t>村镇银行</t>
   </si>
   <si>
     <t>排除关键字</t>
@@ -2942,8 +2984,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
@@ -2978,120 +3020,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="13"/>
       <color theme="3"/>
@@ -3109,7 +3037,35 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -3117,6 +3073,92 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -3143,13 +3185,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3161,49 +3215,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3221,13 +3239,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3245,7 +3269,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3257,25 +3323,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3287,43 +3359,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3354,20 +3396,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3383,6 +3414,21 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3411,30 +3457,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -3449,16 +3471,36 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3467,133 +3509,133 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="24" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -3970,10 +4012,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="13.7787610619469" customWidth="1"/>
-    <col min="2" max="2" width="28.4424778761062" customWidth="1"/>
+    <col min="1" max="1" width="13.7818181818182" customWidth="1"/>
+    <col min="2" max="2" width="28.4454545454545" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4096,29 +4138,29 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="2" outlineLevelCol="7"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>29</v>
       </c>
       <c r="B1" t="s">
-        <v>462</v>
+        <v>476</v>
       </c>
       <c r="C1" t="s">
-        <v>463</v>
+        <v>477</v>
       </c>
       <c r="D1" t="s">
-        <v>464</v>
+        <v>478</v>
       </c>
       <c r="E1" t="s">
-        <v>465</v>
+        <v>479</v>
       </c>
       <c r="F1" t="s">
-        <v>466</v>
+        <v>480</v>
       </c>
       <c r="G1" t="s">
-        <v>467</v>
+        <v>481</v>
       </c>
       <c r="H1" t="s">
         <v>2</v>
@@ -4126,39 +4168,39 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B2" t="s">
-        <v>468</v>
+        <v>482</v>
       </c>
       <c r="C2" t="s">
-        <v>469</v>
+        <v>483</v>
       </c>
       <c r="D2" t="s">
-        <v>418</v>
+        <v>433</v>
       </c>
       <c r="E2" t="s">
-        <v>459</v>
+        <v>473</v>
       </c>
       <c r="H2" t="s">
-        <v>470</v>
+        <v>484</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B3" t="s">
-        <v>468</v>
+        <v>482</v>
       </c>
       <c r="D3" t="s">
-        <v>471</v>
+        <v>485</v>
       </c>
       <c r="E3" t="s">
-        <v>460</v>
+        <v>474</v>
       </c>
       <c r="H3" t="s">
-        <v>472</v>
+        <v>486</v>
       </c>
     </row>
   </sheetData>
@@ -4172,17 +4214,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="3"/>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>29</v>
       </c>
       <c r="B1" t="s">
-        <v>473</v>
+        <v>487</v>
       </c>
       <c r="C1" t="s">
-        <v>451</v>
+        <v>465</v>
       </c>
       <c r="D1" t="s">
         <v>2</v>
@@ -4190,44 +4232,44 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B2" t="s">
-        <v>474</v>
+        <v>488</v>
       </c>
       <c r="C2" t="s">
-        <v>475</v>
+        <v>489</v>
       </c>
       <c r="D2" t="s">
-        <v>476</v>
+        <v>490</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B3" t="s">
-        <v>477</v>
+        <v>491</v>
       </c>
       <c r="C3" t="s">
-        <v>478</v>
+        <v>492</v>
       </c>
       <c r="D3" t="s">
-        <v>479</v>
+        <v>493</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B4" t="s">
-        <v>480</v>
+        <v>494</v>
       </c>
       <c r="C4" t="s">
-        <v>481</v>
+        <v>495</v>
       </c>
       <c r="D4" t="s">
-        <v>482</v>
+        <v>496</v>
       </c>
     </row>
   </sheetData>
@@ -4241,7 +4283,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:J4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -4258,28 +4300,28 @@
         <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>483</v>
+        <v>497</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>484</v>
+        <v>498</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>485</v>
+        <v>499</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>486</v>
+        <v>500</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>487</v>
+        <v>501</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>488</v>
+        <v>502</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>489</v>
+        <v>503</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>490</v>
+        <v>504</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>2</v>
@@ -4287,98 +4329,98 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>491</v>
+        <v>505</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>492</v>
+        <v>506</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>493</v>
+        <v>507</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>491</v>
+        <v>505</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>494</v>
+        <v>508</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>495</v>
+        <v>509</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>474</v>
+        <v>488</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>496</v>
+        <v>510</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>491</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>494</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>477</v>
-      </c>
       <c r="I3" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>498</v>
+        <v>512</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>491</v>
+        <v>505</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>492</v>
+        <v>506</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>493</v>
+        <v>507</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>491</v>
+        <v>505</v>
       </c>
       <c r="F4" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>494</v>
       </c>
-      <c r="G4" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>480</v>
-      </c>
       <c r="I4" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>500</v>
+        <v>514</v>
       </c>
     </row>
   </sheetData>
@@ -4394,12 +4436,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:R18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="3" max="3" width="31.0442477876106" customWidth="1"/>
-    <col min="14" max="14" width="14.7787610619469" customWidth="1"/>
-    <col min="15" max="15" width="12.8849557522124" customWidth="1"/>
+    <col min="3" max="3" width="31.0454545454545" customWidth="1"/>
+    <col min="14" max="14" width="14.7818181818182" customWidth="1"/>
+    <col min="15" max="15" width="12.8818181818182" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
@@ -4847,20 +4889,20 @@
       <c r="O15" s="6"/>
     </row>
     <row r="16" spans="1:18">
-      <c r="A16" t="s">
+      <c r="A16" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" t="s">
         <v>86</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>87</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>88</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>89</v>
-      </c>
-      <c r="E16" t="s">
-        <v>90</v>
       </c>
       <c r="F16" t="s">
         <v>62</v>
@@ -4872,16 +4914,104 @@
         <v>51</v>
       </c>
       <c r="N16" t="s">
+        <v>90</v>
+      </c>
+      <c r="O16" t="s">
         <v>91</v>
       </c>
-      <c r="O16" t="s">
-        <v>92</v>
-      </c>
       <c r="P16" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="R16" t="s">
         <v>93</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18">
+      <c r="A17" t="s">
+        <v>92</v>
+      </c>
+      <c r="B17" t="s">
+        <v>94</v>
+      </c>
+      <c r="C17" t="s">
+        <v>95</v>
+      </c>
+      <c r="D17" t="s">
+        <v>96</v>
+      </c>
+      <c r="E17" t="s">
+        <v>89</v>
+      </c>
+      <c r="F17">
+        <v>7</v>
+      </c>
+      <c r="I17">
+        <v>8</v>
+      </c>
+      <c r="J17">
+        <v>16</v>
+      </c>
+      <c r="K17" t="s">
+        <v>51</v>
+      </c>
+      <c r="L17" t="s">
+        <v>97</v>
+      </c>
+      <c r="N17" t="s">
+        <v>98</v>
+      </c>
+      <c r="O17" t="s">
+        <v>99</v>
+      </c>
+      <c r="P17" t="s">
+        <v>92</v>
+      </c>
+      <c r="R17" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18">
+      <c r="A18" t="s">
+        <v>92</v>
+      </c>
+      <c r="B18" t="s">
+        <v>101</v>
+      </c>
+      <c r="C18" t="s">
+        <v>95</v>
+      </c>
+      <c r="D18" t="s">
+        <v>96</v>
+      </c>
+      <c r="E18" t="s">
+        <v>89</v>
+      </c>
+      <c r="F18">
+        <v>24</v>
+      </c>
+      <c r="I18">
+        <v>25</v>
+      </c>
+      <c r="J18">
+        <v>29</v>
+      </c>
+      <c r="K18" t="s">
+        <v>51</v>
+      </c>
+      <c r="L18" t="s">
+        <v>97</v>
+      </c>
+      <c r="N18" t="s">
+        <v>98</v>
+      </c>
+      <c r="O18" t="s">
+        <v>102</v>
+      </c>
+      <c r="P18" t="s">
+        <v>92</v>
+      </c>
+      <c r="R18" t="s">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -4895,17 +5025,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:K147"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="10" t="s">
         <v>29</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="D1" s="10" t="s">
         <v>31</v>
@@ -4914,16 +5044,16 @@
         <v>32</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="I1" s="10" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="J1" s="10" t="s">
         <v>2</v>
@@ -4931,10 +5061,10 @@
     </row>
     <row r="2" s="9" customFormat="1" spans="1:10">
       <c r="A2" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="C2" s="11" t="s">
         <v>59</v>
@@ -4946,27 +5076,27 @@
         <v>61</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" s="9" customFormat="1" spans="1:10">
       <c r="A3" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="C3" s="11" t="s">
         <v>59</v>
@@ -4978,27 +5108,27 @@
         <v>61</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" s="9" customFormat="1" spans="1:10">
       <c r="A4" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>59</v>
@@ -5010,27 +5140,27 @@
         <v>61</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" s="9" customFormat="1" spans="1:10">
       <c r="A5" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>59</v>
@@ -5042,27 +5172,27 @@
         <v>61</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="J5" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="6" s="9" customFormat="1" spans="1:10">
       <c r="A6" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>59</v>
@@ -5074,27 +5204,27 @@
         <v>61</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="J6" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7" s="9" customFormat="1" spans="1:10">
       <c r="A7" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>59</v>
@@ -5106,27 +5236,27 @@
         <v>61</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="8" s="9" customFormat="1" spans="1:10">
       <c r="A8" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>59</v>
@@ -5138,27 +5268,27 @@
         <v>61</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="9" s="9" customFormat="1" spans="1:10">
       <c r="A9" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>59</v>
@@ -5170,27 +5300,27 @@
         <v>61</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="J9" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10" s="9" customFormat="1" spans="1:10">
       <c r="A10" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>59</v>
@@ -5202,27 +5332,27 @@
         <v>61</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="11" s="9" customFormat="1" spans="1:10">
       <c r="A11" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>59</v>
@@ -5234,24 +5364,24 @@
         <v>61</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B12" t="s">
         <v>54</v>
@@ -5266,24 +5396,24 @@
         <v>55</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B13" t="s">
         <v>54</v>
@@ -5298,24 +5428,24 @@
         <v>55</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B14" t="s">
         <v>54</v>
@@ -5330,24 +5460,24 @@
         <v>55</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B15" t="s">
         <v>54</v>
@@ -5362,24 +5492,24 @@
         <v>55</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B16" t="s">
         <v>54</v>
@@ -5394,24 +5524,24 @@
         <v>55</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B17" t="s">
         <v>54</v>
@@ -5426,24 +5556,24 @@
         <v>55</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B18" t="s">
         <v>54</v>
@@ -5458,24 +5588,24 @@
         <v>55</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G18" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="J18" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B19" t="s">
         <v>54</v>
@@ -5490,24 +5620,24 @@
         <v>55</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B20" t="s">
         <v>54</v>
@@ -5522,24 +5652,24 @@
         <v>55</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B21" t="s">
         <v>54</v>
@@ -5554,24 +5684,24 @@
         <v>55</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B22" t="s">
         <v>54</v>
@@ -5586,24 +5716,24 @@
         <v>55</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G22" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B23" t="s">
         <v>54</v>
@@ -5618,24 +5748,24 @@
         <v>55</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B24" t="s">
         <v>54</v>
@@ -5650,24 +5780,24 @@
         <v>55</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G24" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="J24" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B25" t="s">
         <v>54</v>
@@ -5682,24 +5812,24 @@
         <v>55</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="J25" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B26" t="s">
         <v>54</v>
@@ -5714,24 +5844,24 @@
         <v>55</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G26" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B27" t="s">
         <v>54</v>
@@ -5746,24 +5876,24 @@
         <v>55</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="J27" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B28" t="s">
         <v>54</v>
@@ -5778,24 +5908,24 @@
         <v>55</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G28" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="J28" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B29" t="s">
         <v>54</v>
@@ -5810,24 +5940,24 @@
         <v>55</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="I29" s="9" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="J29" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B30" t="s">
         <v>54</v>
@@ -5842,24 +5972,24 @@
         <v>55</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G30" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="I30" s="9" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="J30" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B31" t="s">
         <v>54</v>
@@ -5874,24 +6004,24 @@
         <v>55</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="I31" s="9" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="J31" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="32" spans="1:10">
       <c r="A32" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B32" t="s">
         <v>54</v>
@@ -5906,24 +6036,24 @@
         <v>55</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G32" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H32" s="9" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="I32" s="9" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="J32" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="33" spans="1:10">
       <c r="A33" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B33" t="s">
         <v>54</v>
@@ -5938,24 +6068,24 @@
         <v>55</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="I33" s="9" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="J33" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="34" spans="1:10">
       <c r="A34" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B34" t="s">
         <v>54</v>
@@ -5970,24 +6100,24 @@
         <v>55</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G34" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H34" s="9" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="I34" s="9" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="J34" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="35" spans="1:10">
       <c r="A35" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B35" t="s">
         <v>54</v>
@@ -6002,24 +6132,24 @@
         <v>55</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="I35" s="9" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="J35" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="36" spans="1:10">
       <c r="A36" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B36" t="s">
         <v>54</v>
@@ -6034,24 +6164,24 @@
         <v>55</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G36" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H36" s="9" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="I36" s="9" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="J36" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="37" spans="1:10">
       <c r="A37" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B37" t="s">
         <v>54</v>
@@ -6066,24 +6196,24 @@
         <v>55</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="I37" s="9" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="J37" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="38" spans="1:10">
       <c r="A38" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B38" t="s">
         <v>54</v>
@@ -6098,24 +6228,24 @@
         <v>55</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G38" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H38" s="9" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="I38" s="9" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="J38" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="39" spans="1:10">
       <c r="A39" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B39" t="s">
         <v>54</v>
@@ -6130,24 +6260,24 @@
         <v>55</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="I39" s="9" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="J39" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="40" spans="1:10">
       <c r="A40" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B40" t="s">
         <v>54</v>
@@ -6162,24 +6292,24 @@
         <v>55</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G40" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H40" s="9" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="I40" s="9" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="J40" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="41" spans="1:10">
       <c r="A41" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B41" t="s">
         <v>54</v>
@@ -6194,24 +6324,24 @@
         <v>55</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="I41" s="9" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="J41" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="42" spans="1:10">
       <c r="A42" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B42" t="s">
         <v>54</v>
@@ -6226,24 +6356,24 @@
         <v>55</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G42" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H42" s="9" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="I42" s="9" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="J42" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="43" spans="1:10">
       <c r="A43" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B43" t="s">
         <v>54</v>
@@ -6258,24 +6388,24 @@
         <v>55</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="I43" s="9" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="J43" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="44" spans="1:10">
       <c r="A44" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B44" t="s">
         <v>54</v>
@@ -6290,24 +6420,24 @@
         <v>55</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G44" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H44" s="9" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="I44" s="9" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="J44" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="45" spans="1:10">
       <c r="A45" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B45" t="s">
         <v>54</v>
@@ -6322,24 +6452,24 @@
         <v>55</v>
       </c>
       <c r="F45" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="I45" s="9" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="J45" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="46" spans="1:10">
       <c r="A46" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B46" t="s">
         <v>54</v>
@@ -6354,24 +6484,24 @@
         <v>55</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G46" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H46" s="9" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="I46" s="9" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="J46" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="47" spans="1:10">
       <c r="A47" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B47" t="s">
         <v>54</v>
@@ -6386,24 +6516,24 @@
         <v>55</v>
       </c>
       <c r="F47" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="I47" s="9" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="J47" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="48" spans="1:10">
       <c r="A48" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B48" t="s">
         <v>54</v>
@@ -6418,24 +6548,24 @@
         <v>55</v>
       </c>
       <c r="F48" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G48" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H48" s="9" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="I48" s="9" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="J48" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="49" spans="1:10">
       <c r="A49" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B49" t="s">
         <v>54</v>
@@ -6450,24 +6580,24 @@
         <v>55</v>
       </c>
       <c r="F49" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="I49" s="9" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="J49" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="50" spans="1:10">
       <c r="A50" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B50" t="s">
         <v>54</v>
@@ -6482,24 +6612,24 @@
         <v>55</v>
       </c>
       <c r="F50" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G50" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H50" s="9" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="I50" s="9" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="J50" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="51" spans="1:10">
       <c r="A51" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B51" t="s">
         <v>54</v>
@@ -6514,24 +6644,24 @@
         <v>55</v>
       </c>
       <c r="F51" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="I51" s="9" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="J51" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="52" spans="1:10">
       <c r="A52" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B52" t="s">
         <v>54</v>
@@ -6546,24 +6676,24 @@
         <v>55</v>
       </c>
       <c r="F52" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G52" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H52" s="9" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="I52" s="9" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="J52" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="53" spans="1:10">
       <c r="A53" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B53" t="s">
         <v>54</v>
@@ -6578,24 +6708,24 @@
         <v>55</v>
       </c>
       <c r="F53" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="I53" s="9" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="J53" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="54" spans="1:10">
       <c r="A54" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B54" t="s">
         <v>54</v>
@@ -6610,24 +6740,24 @@
         <v>55</v>
       </c>
       <c r="F54" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G54" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H54" s="9" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="I54" s="9" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="J54" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="55" spans="1:10">
       <c r="A55" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B55" t="s">
         <v>54</v>
@@ -6642,24 +6772,24 @@
         <v>55</v>
       </c>
       <c r="F55" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="I55" s="9" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="J55" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="56" spans="1:11">
       <c r="A56" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B56" t="s">
         <v>54</v>
@@ -6674,25 +6804,25 @@
         <v>55</v>
       </c>
       <c r="F56" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G56" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H56" s="11" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="I56" s="9" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="J56" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="K56" s="9"/>
     </row>
     <row r="57" spans="1:10">
       <c r="A57" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B57" t="s">
         <v>54</v>
@@ -6707,24 +6837,24 @@
         <v>55</v>
       </c>
       <c r="F57" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="I57" s="9" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="J57" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="58" spans="1:10">
       <c r="A58" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B58" t="s">
         <v>54</v>
@@ -6739,24 +6869,24 @@
         <v>55</v>
       </c>
       <c r="F58" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G58" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H58" s="9" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="I58" s="9" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="J58" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="59" spans="1:10">
       <c r="A59" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B59" t="s">
         <v>54</v>
@@ -6771,24 +6901,24 @@
         <v>55</v>
       </c>
       <c r="F59" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="I59" s="9" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="J59" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="60" spans="1:10">
       <c r="A60" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B60" t="s">
         <v>54</v>
@@ -6803,24 +6933,24 @@
         <v>55</v>
       </c>
       <c r="F60" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G60" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H60" s="9" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="I60" s="9" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="J60" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="61" spans="1:10">
       <c r="A61" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B61" t="s">
         <v>54</v>
@@ -6835,24 +6965,24 @@
         <v>55</v>
       </c>
       <c r="F61" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="I61" s="9" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="J61" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="62" spans="1:10">
       <c r="A62" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B62" t="s">
         <v>54</v>
@@ -6867,24 +6997,24 @@
         <v>55</v>
       </c>
       <c r="F62" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G62" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H62" s="9" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="I62" s="9" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="J62" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="63" spans="1:10">
       <c r="A63" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B63" t="s">
         <v>54</v>
@@ -6899,24 +7029,24 @@
         <v>55</v>
       </c>
       <c r="F63" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="I63" s="9" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="J63" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="64" spans="1:10">
       <c r="A64" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B64" t="s">
         <v>54</v>
@@ -6931,24 +7061,24 @@
         <v>55</v>
       </c>
       <c r="F64" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G64" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H64" s="9" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="I64" s="9" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="J64" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="65" spans="1:10">
       <c r="A65" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B65" t="s">
         <v>54</v>
@@ -6963,24 +7093,24 @@
         <v>55</v>
       </c>
       <c r="F65" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="I65" s="9" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="J65" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="66" spans="1:10">
       <c r="A66" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B66" t="s">
         <v>54</v>
@@ -6995,24 +7125,24 @@
         <v>55</v>
       </c>
       <c r="F66" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G66" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H66" s="9" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="I66" s="9" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="J66" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="67" spans="1:10">
       <c r="A67" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B67" t="s">
         <v>54</v>
@@ -7027,24 +7157,24 @@
         <v>55</v>
       </c>
       <c r="F67" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="I67" s="9" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="J67" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="68" spans="1:10">
       <c r="A68" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B68" t="s">
         <v>54</v>
@@ -7059,24 +7189,24 @@
         <v>55</v>
       </c>
       <c r="F68" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G68" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H68" s="9" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="I68" s="9" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="J68" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="69" spans="1:10">
       <c r="A69" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B69" t="s">
         <v>54</v>
@@ -7091,24 +7221,24 @@
         <v>55</v>
       </c>
       <c r="F69" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="I69" s="9" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="J69" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="70" spans="1:10">
       <c r="A70" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B70" t="s">
         <v>54</v>
@@ -7123,24 +7253,24 @@
         <v>55</v>
       </c>
       <c r="F70" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G70" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H70" s="9" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="I70" s="9" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="J70" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="71" spans="1:10">
       <c r="A71" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B71" t="s">
         <v>54</v>
@@ -7155,24 +7285,24 @@
         <v>55</v>
       </c>
       <c r="F71" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="I71" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="J71" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="72" spans="1:10">
       <c r="A72" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B72" t="s">
         <v>54</v>
@@ -7187,24 +7317,24 @@
         <v>55</v>
       </c>
       <c r="F72" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G72" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H72" s="9" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="I72" s="9" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="J72" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="73" spans="1:10">
       <c r="A73" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B73" t="s">
         <v>54</v>
@@ -7219,24 +7349,24 @@
         <v>55</v>
       </c>
       <c r="F73" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="I73" s="9" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="J73" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="74" spans="1:10">
       <c r="A74" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B74" t="s">
         <v>54</v>
@@ -7251,24 +7381,24 @@
         <v>55</v>
       </c>
       <c r="F74" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G74" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H74" s="9" t="s">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="I74" s="9" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="J74" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="75" spans="1:10">
       <c r="A75" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B75" t="s">
         <v>54</v>
@@ -7283,24 +7413,24 @@
         <v>55</v>
       </c>
       <c r="F75" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="I75" s="9" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="J75" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="76" spans="1:10">
       <c r="A76" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B76" t="s">
         <v>54</v>
@@ -7315,24 +7445,24 @@
         <v>55</v>
       </c>
       <c r="F76" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G76" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H76" s="9" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="I76" s="9" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="J76" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="77" spans="1:10">
       <c r="A77" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B77" t="s">
         <v>54</v>
@@ -7347,24 +7477,24 @@
         <v>55</v>
       </c>
       <c r="F77" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="I77" s="9" t="s">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="J77" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="78" spans="1:10">
       <c r="A78" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B78" t="s">
         <v>57</v>
@@ -7379,24 +7509,24 @@
         <v>58</v>
       </c>
       <c r="F78" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G78" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H78" s="9" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="I78" s="9" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="J78" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="79" spans="1:10">
       <c r="A79" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B79" t="s">
         <v>57</v>
@@ -7411,24 +7541,24 @@
         <v>58</v>
       </c>
       <c r="F79" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H79" s="9" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="I79" s="9" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="J79" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="80" spans="1:10">
       <c r="A80" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B80" t="s">
         <v>57</v>
@@ -7443,24 +7573,24 @@
         <v>58</v>
       </c>
       <c r="F80" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G80" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H80" s="9" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="I80" s="9" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="J80" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="81" spans="1:10">
       <c r="A81" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B81" t="s">
         <v>57</v>
@@ -7475,24 +7605,24 @@
         <v>58</v>
       </c>
       <c r="F81" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="I81" s="9" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="J81" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="82" spans="1:10">
       <c r="A82" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B82" t="s">
         <v>57</v>
@@ -7507,24 +7637,24 @@
         <v>58</v>
       </c>
       <c r="F82" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G82" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H82" s="9" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="I82" s="9" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="J82" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="83" spans="1:10">
       <c r="A83" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B83" t="s">
         <v>57</v>
@@ -7539,24 +7669,24 @@
         <v>58</v>
       </c>
       <c r="F83" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="I83" s="9" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="J83" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="84" spans="1:10">
       <c r="A84" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B84" t="s">
         <v>57</v>
@@ -7571,24 +7701,24 @@
         <v>58</v>
       </c>
       <c r="F84" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G84" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H84" s="9" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="I84" s="9" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="J84" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="85" spans="1:10">
       <c r="A85" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B85" t="s">
         <v>57</v>
@@ -7603,24 +7733,24 @@
         <v>58</v>
       </c>
       <c r="F85" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H85" s="9" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="I85" s="9" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="J85" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="86" spans="1:10">
       <c r="A86" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B86" t="s">
         <v>57</v>
@@ -7635,24 +7765,24 @@
         <v>58</v>
       </c>
       <c r="F86" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G86" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H86" s="9" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="I86" s="9" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="J86" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="87" spans="1:10">
       <c r="A87" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B87" t="s">
         <v>57</v>
@@ -7667,24 +7797,24 @@
         <v>58</v>
       </c>
       <c r="F87" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G87" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H87" s="9" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="I87" s="9" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="J87" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="88" spans="1:10">
       <c r="A88" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B88" t="s">
         <v>57</v>
@@ -7699,24 +7829,24 @@
         <v>58</v>
       </c>
       <c r="F88" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G88" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H88" s="9" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="I88" s="9" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="J88" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="89" spans="1:10">
       <c r="A89" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B89" t="s">
         <v>57</v>
@@ -7731,24 +7861,24 @@
         <v>58</v>
       </c>
       <c r="F89" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H89" s="9" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="I89" s="9" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="J89" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="90" spans="1:10">
       <c r="A90" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B90" t="s">
         <v>57</v>
@@ -7763,24 +7893,24 @@
         <v>58</v>
       </c>
       <c r="F90" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G90" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H90" s="9" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="I90" s="9" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="J90" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="91" spans="1:10">
       <c r="A91" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B91" t="s">
         <v>57</v>
@@ -7795,24 +7925,24 @@
         <v>58</v>
       </c>
       <c r="F91" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G91" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H91" s="9" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="I91" s="9" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="J91" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="92" spans="1:10">
       <c r="A92" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B92" t="s">
         <v>57</v>
@@ -7827,24 +7957,24 @@
         <v>58</v>
       </c>
       <c r="F92" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G92" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H92" s="9" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="I92" s="9" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="J92" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="93" spans="1:10">
       <c r="A93" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B93" t="s">
         <v>57</v>
@@ -7859,24 +7989,24 @@
         <v>58</v>
       </c>
       <c r="F93" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G93" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H93" s="9" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="I93" s="9" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="J93" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="94" spans="1:10">
       <c r="A94" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B94" t="s">
         <v>57</v>
@@ -7891,24 +8021,24 @@
         <v>58</v>
       </c>
       <c r="F94" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G94" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H94" s="9" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="I94" s="9" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="J94" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="95" spans="1:10">
       <c r="A95" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B95" t="s">
         <v>57</v>
@@ -7923,24 +8053,24 @@
         <v>58</v>
       </c>
       <c r="F95" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G95" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H95" s="9" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="I95" s="9" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="J95" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="96" spans="1:10">
       <c r="A96" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B96" t="s">
         <v>57</v>
@@ -7955,24 +8085,24 @@
         <v>58</v>
       </c>
       <c r="F96" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G96" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H96" s="9" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="I96" s="9" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="J96" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="97" spans="1:10">
       <c r="A97" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B97" t="s">
         <v>57</v>
@@ -7987,24 +8117,24 @@
         <v>58</v>
       </c>
       <c r="F97" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G97" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H97" s="9" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="I97" s="9" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="J97" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="98" spans="1:10">
       <c r="A98" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B98" t="s">
         <v>57</v>
@@ -8019,24 +8149,24 @@
         <v>58</v>
       </c>
       <c r="F98" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G98" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H98" s="9" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="I98" s="9" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="J98" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="99" spans="1:10">
       <c r="A99" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B99" t="s">
         <v>57</v>
@@ -8051,24 +8181,24 @@
         <v>58</v>
       </c>
       <c r="F99" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G99" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H99" s="9" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="I99" s="9" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="J99" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="100" spans="1:10">
       <c r="A100" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B100" t="s">
         <v>57</v>
@@ -8083,24 +8213,24 @@
         <v>58</v>
       </c>
       <c r="F100" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G100" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H100" s="9" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="I100" s="9" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="J100" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="101" spans="1:10">
       <c r="A101" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B101" t="s">
         <v>57</v>
@@ -8115,24 +8245,24 @@
         <v>58</v>
       </c>
       <c r="F101" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G101" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H101" s="9" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="I101" s="9" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="J101" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="102" spans="1:10">
       <c r="A102" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B102" t="s">
         <v>57</v>
@@ -8147,24 +8277,24 @@
         <v>58</v>
       </c>
       <c r="F102" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G102" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H102" s="9" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="I102" s="9" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="J102" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="103" spans="1:10">
       <c r="A103" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B103" t="s">
         <v>57</v>
@@ -8179,24 +8309,24 @@
         <v>58</v>
       </c>
       <c r="F103" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G103" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H103" s="9" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="I103" s="9" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="J103" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="104" spans="1:10">
       <c r="A104" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B104" t="s">
         <v>57</v>
@@ -8211,24 +8341,24 @@
         <v>58</v>
       </c>
       <c r="F104" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G104" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H104" s="9" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="I104" s="9" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="J104" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="105" spans="1:10">
       <c r="A105" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B105" t="s">
         <v>57</v>
@@ -8243,24 +8373,24 @@
         <v>58</v>
       </c>
       <c r="F105" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G105" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H105" s="9" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="I105" s="9" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="J105" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="106" spans="1:10">
       <c r="A106" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B106" t="s">
         <v>57</v>
@@ -8275,24 +8405,24 @@
         <v>58</v>
       </c>
       <c r="F106" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G106" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H106" s="9" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="I106" s="9" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="J106" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="107" spans="1:10">
       <c r="A107" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B107" t="s">
         <v>57</v>
@@ -8307,24 +8437,24 @@
         <v>58</v>
       </c>
       <c r="F107" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G107" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H107" s="9" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="I107" s="9" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="J107" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="108" spans="1:10">
       <c r="A108" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B108" t="s">
         <v>57</v>
@@ -8339,24 +8469,24 @@
         <v>58</v>
       </c>
       <c r="F108" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G108" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H108" s="9" t="s">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="I108" s="9" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="J108" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="109" spans="1:10">
       <c r="A109" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B109" t="s">
         <v>57</v>
@@ -8371,24 +8501,24 @@
         <v>58</v>
       </c>
       <c r="F109" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G109" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H109" s="9" t="s">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="I109" s="9" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="J109" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="110" spans="1:10">
       <c r="A110" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B110" t="s">
         <v>57</v>
@@ -8403,24 +8533,24 @@
         <v>58</v>
       </c>
       <c r="F110" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G110" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H110" s="9" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="I110" s="9" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="J110" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="111" spans="1:10">
       <c r="A111" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B111" t="s">
         <v>57</v>
@@ -8435,24 +8565,24 @@
         <v>58</v>
       </c>
       <c r="F111" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G111" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H111" s="9" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="I111" s="9" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="J111" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="112" spans="1:10">
       <c r="A112" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B112" t="s">
         <v>57</v>
@@ -8467,24 +8597,24 @@
         <v>58</v>
       </c>
       <c r="F112" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G112" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H112" s="9" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="I112" s="9" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="J112" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="113" spans="1:10">
       <c r="A113" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B113" t="s">
         <v>57</v>
@@ -8499,24 +8629,24 @@
         <v>58</v>
       </c>
       <c r="F113" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G113" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H113" s="9" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="I113" s="9" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="J113" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="114" spans="1:10">
       <c r="A114" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B114" t="s">
         <v>57</v>
@@ -8531,24 +8661,24 @@
         <v>58</v>
       </c>
       <c r="F114" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G114" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H114" s="9" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="I114" s="9" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="J114" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="115" spans="1:10">
       <c r="A115" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B115" t="s">
         <v>57</v>
@@ -8563,24 +8693,24 @@
         <v>58</v>
       </c>
       <c r="F115" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G115" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H115" s="9" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="I115" s="9" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="J115" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="116" spans="1:10">
       <c r="A116" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B116" t="s">
         <v>57</v>
@@ -8595,24 +8725,24 @@
         <v>58</v>
       </c>
       <c r="F116" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G116" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H116" s="9" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="I116" s="9" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="J116" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="117" spans="1:10">
       <c r="A117" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B117" t="s">
         <v>57</v>
@@ -8627,24 +8757,24 @@
         <v>58</v>
       </c>
       <c r="F117" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G117" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H117" s="9" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="I117" s="9" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="J117" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="118" spans="1:10">
       <c r="A118" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B118" t="s">
         <v>57</v>
@@ -8659,24 +8789,24 @@
         <v>58</v>
       </c>
       <c r="F118" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G118" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H118" s="9" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="I118" s="9" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="J118" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="119" spans="1:10">
       <c r="A119" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B119" t="s">
         <v>57</v>
@@ -8691,24 +8821,24 @@
         <v>58</v>
       </c>
       <c r="F119" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G119" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H119" s="9" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="I119" s="9" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="J119" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="120" spans="1:10">
       <c r="A120" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B120" t="s">
         <v>57</v>
@@ -8723,24 +8853,24 @@
         <v>58</v>
       </c>
       <c r="F120" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G120" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H120" s="9" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="I120" s="9" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="J120" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="121" spans="1:10">
       <c r="A121" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B121" t="s">
         <v>57</v>
@@ -8755,24 +8885,24 @@
         <v>58</v>
       </c>
       <c r="F121" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G121" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H121" s="9" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="I121" s="9" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="J121" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="122" spans="1:10">
       <c r="A122" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B122" t="s">
         <v>57</v>
@@ -8787,24 +8917,24 @@
         <v>58</v>
       </c>
       <c r="F122" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G122" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H122" s="9" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="I122" s="9" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="J122" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="123" spans="1:10">
       <c r="A123" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B123" t="s">
         <v>57</v>
@@ -8819,24 +8949,24 @@
         <v>58</v>
       </c>
       <c r="F123" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G123" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H123" s="9" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="I123" s="9" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="J123" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="124" spans="1:10">
       <c r="A124" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B124" t="s">
         <v>57</v>
@@ -8851,24 +8981,24 @@
         <v>58</v>
       </c>
       <c r="F124" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G124" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H124" s="9" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="I124" s="9" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="J124" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="125" spans="1:10">
       <c r="A125" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B125" t="s">
         <v>57</v>
@@ -8883,24 +9013,24 @@
         <v>58</v>
       </c>
       <c r="F125" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G125" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H125" s="9" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="I125" s="9" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="J125" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="126" spans="1:10">
       <c r="A126" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B126" t="s">
         <v>57</v>
@@ -8915,24 +9045,24 @@
         <v>58</v>
       </c>
       <c r="F126" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G126" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H126" s="9" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="I126" s="9" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="J126" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="127" spans="1:10">
       <c r="A127" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B127" t="s">
         <v>57</v>
@@ -8947,24 +9077,24 @@
         <v>58</v>
       </c>
       <c r="F127" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G127" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H127" s="9" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="I127" s="9" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="J127" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="128" spans="1:10">
       <c r="A128" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B128" t="s">
         <v>57</v>
@@ -8979,24 +9109,24 @@
         <v>58</v>
       </c>
       <c r="F128" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G128" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H128" s="9" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="I128" s="9" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="J128" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="129" spans="1:10">
       <c r="A129" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B129" t="s">
         <v>57</v>
@@ -9011,24 +9141,24 @@
         <v>58</v>
       </c>
       <c r="F129" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G129" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H129" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="I129" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="J129" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="130" spans="1:10">
       <c r="A130" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B130" t="s">
         <v>57</v>
@@ -9043,24 +9173,24 @@
         <v>58</v>
       </c>
       <c r="F130" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G130" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H130" s="9" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="I130" s="9" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="J130" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="131" spans="1:10">
       <c r="A131" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B131" t="s">
         <v>57</v>
@@ -9075,24 +9205,24 @@
         <v>58</v>
       </c>
       <c r="F131" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G131" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H131" s="9" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="I131" s="9" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="J131" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="132" spans="1:10">
       <c r="A132" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B132" t="s">
         <v>57</v>
@@ -9107,24 +9237,24 @@
         <v>58</v>
       </c>
       <c r="F132" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G132" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H132" s="9" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="I132" s="9" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="J132" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="133" spans="1:10">
       <c r="A133" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B133" t="s">
         <v>57</v>
@@ -9139,24 +9269,24 @@
         <v>58</v>
       </c>
       <c r="F133" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G133" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H133" s="9" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="I133" s="9" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="J133" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="134" spans="1:10">
       <c r="A134" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B134" t="s">
         <v>57</v>
@@ -9171,24 +9301,24 @@
         <v>58</v>
       </c>
       <c r="F134" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G134" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H134" s="9" t="s">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="I134" s="9" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="J134" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="135" spans="1:10">
       <c r="A135" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B135" t="s">
         <v>57</v>
@@ -9203,24 +9333,24 @@
         <v>58</v>
       </c>
       <c r="F135" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G135" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H135" s="9" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="I135" s="9" t="s">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="J135" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="136" spans="1:10">
       <c r="A136" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B136" t="s">
         <v>57</v>
@@ -9235,24 +9365,24 @@
         <v>58</v>
       </c>
       <c r="F136" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G136" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H136" s="9" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="I136" s="9" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="J136" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="137" spans="1:10">
       <c r="A137" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B137" t="s">
         <v>57</v>
@@ -9267,24 +9397,24 @@
         <v>58</v>
       </c>
       <c r="F137" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G137" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H137" s="9" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="I137" s="9" t="s">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="J137" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="138" spans="1:10">
       <c r="A138" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B138" t="s">
         <v>57</v>
@@ -9299,24 +9429,24 @@
         <v>58</v>
       </c>
       <c r="F138" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G138" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H138" s="9" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="I138" s="9" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="J138" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="139" spans="1:10">
       <c r="A139" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B139" t="s">
         <v>57</v>
@@ -9331,24 +9461,24 @@
         <v>58</v>
       </c>
       <c r="F139" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G139" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H139" s="9" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="I139" s="9" t="s">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="J139" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="140" s="9" customFormat="1" spans="1:10">
       <c r="A140" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B140" s="9" t="s">
         <v>81</v>
@@ -9363,24 +9493,24 @@
         <v>83</v>
       </c>
       <c r="F140" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G140" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H140" s="9" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="I140" s="12" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="J140" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="141" s="9" customFormat="1" spans="1:10">
       <c r="A141" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B141" s="9" t="s">
         <v>81</v>
@@ -9395,24 +9525,24 @@
         <v>83</v>
       </c>
       <c r="F141" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G141" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H141" s="9" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="I141" s="12" t="s">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="J141" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="142" s="9" customFormat="1" spans="1:10">
       <c r="A142" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B142" s="9" t="s">
         <v>81</v>
@@ -9427,24 +9557,24 @@
         <v>83</v>
       </c>
       <c r="F142" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G142" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H142" s="9" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="I142" s="12" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="J142" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="143" s="9" customFormat="1" spans="1:10">
       <c r="A143" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B143" s="9" t="s">
         <v>81</v>
@@ -9459,24 +9589,24 @@
         <v>83</v>
       </c>
       <c r="F143" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G143" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H143" s="9" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="I143" s="12" t="s">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="J143" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="144" s="9" customFormat="1" spans="1:10">
       <c r="A144" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B144" s="9" t="s">
         <v>81</v>
@@ -9491,24 +9621,24 @@
         <v>83</v>
       </c>
       <c r="F144" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G144" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H144" s="9" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="I144" s="12" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="J144" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="145" s="9" customFormat="1" spans="1:10">
       <c r="A145" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B145" s="9" t="s">
         <v>81</v>
@@ -9523,24 +9653,24 @@
         <v>83</v>
       </c>
       <c r="F145" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G145" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H145" s="9" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="I145" s="12" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="J145" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="146" s="9" customFormat="1" spans="1:10">
       <c r="A146" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B146" s="9" t="s">
         <v>81</v>
@@ -9555,24 +9685,24 @@
         <v>83</v>
       </c>
       <c r="F146" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G146" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H146" s="9" t="s">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="I146" s="12" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="J146" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="147" s="9" customFormat="1" spans="1:10">
       <c r="A147" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B147" s="9" t="s">
         <v>81</v>
@@ -9587,19 +9717,19 @@
         <v>83</v>
       </c>
       <c r="F147" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G147" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H147" s="9" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="I147" s="12" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="J147" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -9613,12 +9743,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H18"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="7"/>
   <cols>
-    <col min="2" max="2" width="73.7787610619469" customWidth="1"/>
-    <col min="4" max="4" width="14.2212389380531" customWidth="1"/>
-    <col min="5" max="5" width="62.2212389380531" customWidth="1"/>
-    <col min="6" max="6" width="19.7787610619469" customWidth="1"/>
+    <col min="2" max="2" width="73.7818181818182" customWidth="1"/>
+    <col min="4" max="4" width="14.2181818181818" customWidth="1"/>
+    <col min="5" max="5" width="62.2181818181818" customWidth="1"/>
+    <col min="6" max="6" width="19.7818181818182" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -9626,22 +9756,22 @@
         <v>29</v>
       </c>
       <c r="B1" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="C1" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="D1" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="E1" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="F1" t="s">
         <v>43</v>
       </c>
       <c r="G1" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="H1" t="s">
         <v>2</v>
@@ -9649,22 +9779,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="6" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="C2" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="F2" t="s">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -9672,19 +9802,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="6" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>59</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="F3" s="7" t="s">
         <v>59</v>
@@ -9695,19 +9825,19 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="6" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>48</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>48</v>
@@ -9718,19 +9848,19 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="6" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>54</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>54</v>
@@ -9741,19 +9871,19 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="6" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>57</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>57</v>
@@ -9764,19 +9894,19 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="6" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B7" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>63</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>63</v>
@@ -9787,19 +9917,19 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="6" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B8" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>66</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>66</v>
@@ -9810,19 +9940,19 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="6" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B9" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>69</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>69</v>
@@ -9833,19 +9963,19 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="6" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B10" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>71</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>71</v>
@@ -9856,19 +9986,19 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="6" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B11" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>73</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>73</v>
@@ -9879,19 +10009,19 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="6" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B12" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>75</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>75</v>
@@ -9902,19 +10032,19 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="6" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B13" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>77</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="F13" s="6" t="s">
         <v>77</v>
@@ -9925,19 +10055,19 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="6" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B14" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>79</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>79</v>
@@ -9948,19 +10078,19 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="6" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B15" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>81</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="F15" s="6" t="s">
         <v>81</v>
@@ -9971,19 +10101,19 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="6" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B16" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>84</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>84</v>
@@ -9994,22 +10124,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="6" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="C17" t="s">
+        <v>311</v>
+      </c>
+      <c r="D17" s="6" t="s">
         <v>302</v>
       </c>
-      <c r="D17" s="6" t="s">
-        <v>293</v>
-      </c>
       <c r="E17" s="6" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="F17" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -10017,22 +10147,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="6" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B18" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="C18" t="s">
+        <v>313</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="E18" s="6" t="s">
         <v>303</v>
       </c>
-      <c r="C18" t="s">
-        <v>304</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>293</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>294</v>
-      </c>
       <c r="F18" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -10049,50 +10179,50 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:O1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData>
     <row r="1" spans="1:15">
       <c r="A1" t="s">
         <v>29</v>
       </c>
       <c r="B1" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="C1" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="D1" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="E1" t="s">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="F1" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="G1" t="s">
         <v>43</v>
       </c>
       <c r="H1" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="I1" t="s">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="J1" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="K1" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="L1" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="M1" t="s">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="N1" t="s">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="O1" t="s">
         <v>2</v>
@@ -10108,31 +10238,32 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q62"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:Q66"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="8" max="8" width="15.2212389380531" customWidth="1"/>
-    <col min="9" max="9" width="12.1061946902655" customWidth="1"/>
+    <col min="1" max="1" width="41" customWidth="1"/>
+    <col min="8" max="8" width="15.2181818181818" customWidth="1"/>
+    <col min="9" max="9" width="12.1090909090909" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" t="s">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="B1" t="s">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="C1" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="D1" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="E1" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F1" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G1" t="s">
         <v>0</v>
@@ -10141,28 +10272,28 @@
         <v>1</v>
       </c>
       <c r="I1" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="J1" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="K1" t="s">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c r="L1" t="s">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="M1" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="N1" t="s">
-        <v>327</v>
+        <v>336</v>
       </c>
       <c r="O1" t="s">
-        <v>328</v>
+        <v>337</v>
       </c>
       <c r="P1" t="s">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="Q1" t="s">
         <v>2</v>
@@ -10170,763 +10301,825 @@
     </row>
     <row r="2" spans="1:17">
       <c r="A2" t="s">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="B2" t="s">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="D2" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="E2" t="s">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="G2" t="s">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="H2" t="s">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="I2" t="s">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="J2" t="s">
-        <v>336</v>
+        <v>345</v>
       </c>
       <c r="K2" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="L2" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="O2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="P2" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="Q2" t="s">
-        <v>339</v>
+        <v>348</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="B3" t="s">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="D3" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="E3" t="s">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="G3" t="s">
-        <v>343</v>
-      </c>
-      <c r="H3" s="5">
-        <v>46112</v>
+        <v>352</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>353</v>
       </c>
       <c r="I3" t="s">
-        <v>334</v>
+        <v>354</v>
       </c>
       <c r="J3" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="K3" t="s">
-        <v>345</v>
+        <v>356</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
+        <v>357</v>
+      </c>
+      <c r="B4" t="s">
+        <v>357</v>
+      </c>
+      <c r="D4" t="s">
+        <v>358</v>
+      </c>
+      <c r="E4" t="s">
+        <v>357</v>
+      </c>
+      <c r="I4" t="s">
+        <v>359</v>
+      </c>
+      <c r="J4" t="s">
+        <v>360</v>
+      </c>
+      <c r="K4" t="s">
         <v>346</v>
-      </c>
-      <c r="B4" t="s">
-        <v>346</v>
-      </c>
-      <c r="D4" t="s">
-        <v>347</v>
-      </c>
-      <c r="E4" t="s">
-        <v>346</v>
-      </c>
-      <c r="I4" t="s">
-        <v>348</v>
-      </c>
-      <c r="J4" t="s">
-        <v>349</v>
-      </c>
-      <c r="K4" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="B5" t="s">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="D5" t="s">
-        <v>352</v>
+        <v>363</v>
       </c>
       <c r="E5" t="s">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="J5" t="s">
-        <v>353</v>
+        <v>364</v>
       </c>
       <c r="K5" t="s">
-        <v>345</v>
+        <v>356</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>354</v>
+        <v>365</v>
       </c>
       <c r="B6" t="s">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="D6" t="s">
-        <v>356</v>
+        <v>367</v>
       </c>
       <c r="E6" t="s">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="J6" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
       <c r="K6" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>358</v>
+        <v>369</v>
       </c>
       <c r="B7" t="s">
-        <v>359</v>
+        <v>370</v>
       </c>
       <c r="D7" t="s">
-        <v>360</v>
+        <v>371</v>
       </c>
       <c r="E7" t="s">
-        <v>359</v>
+        <v>370</v>
       </c>
       <c r="J7" t="s">
-        <v>361</v>
+        <v>372</v>
       </c>
       <c r="K7" t="s">
-        <v>345</v>
+        <v>356</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>362</v>
+        <v>373</v>
       </c>
       <c r="B8" t="s">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="D8" t="s">
-        <v>364</v>
+        <v>375</v>
       </c>
       <c r="E8" t="s">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="J8" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
       <c r="K8" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>365</v>
+        <v>376</v>
       </c>
       <c r="B9" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="D9" t="s">
-        <v>367</v>
+        <v>378</v>
       </c>
       <c r="E9" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="J9" t="s">
-        <v>361</v>
+        <v>372</v>
       </c>
       <c r="K9" t="s">
-        <v>345</v>
+        <v>356</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="B10" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="D10" t="s">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="E10" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="J10" t="s">
-        <v>349</v>
+        <v>360</v>
       </c>
       <c r="K10" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>371</v>
+        <v>382</v>
       </c>
       <c r="B11" t="s">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c r="D11">
         <v>3010</v>
       </c>
       <c r="E11" t="s">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c r="J11" t="s">
-        <v>373</v>
+        <v>384</v>
       </c>
       <c r="K11" t="s">
-        <v>345</v>
+        <v>356</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="B12" t="s">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="D12">
         <v>3020</v>
       </c>
       <c r="E12" t="s">
-        <v>375</v>
+        <v>386</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="B13" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="D13">
         <v>3030</v>
       </c>
       <c r="E13" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="B14" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="D14">
         <v>3040</v>
       </c>
       <c r="E14" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>380</v>
+        <v>391</v>
       </c>
       <c r="B15" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="D15">
         <v>4010</v>
       </c>
       <c r="E15" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>382</v>
+        <v>393</v>
       </c>
       <c r="B16" t="s">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="D16">
         <v>4020</v>
       </c>
       <c r="E16" t="s">
-        <v>383</v>
+        <v>394</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="B17" t="s">
-        <v>385</v>
+        <v>396</v>
       </c>
       <c r="D17">
         <v>4030</v>
       </c>
       <c r="E17" t="s">
-        <v>385</v>
+        <v>396</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
       <c r="B18" t="s">
-        <v>387</v>
+        <v>398</v>
       </c>
       <c r="D18">
         <v>4060</v>
       </c>
       <c r="E18" t="s">
-        <v>387</v>
+        <v>398</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" t="s">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c r="B19" t="s">
-        <v>389</v>
+        <v>400</v>
       </c>
       <c r="D19">
         <v>4070</v>
       </c>
       <c r="E19" t="s">
-        <v>389</v>
+        <v>400</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>390</v>
+        <v>401</v>
       </c>
       <c r="B20" t="s">
-        <v>391</v>
+        <v>402</v>
       </c>
       <c r="D20">
         <v>4080</v>
       </c>
       <c r="E20" t="s">
-        <v>391</v>
+        <v>402</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>392</v>
+        <v>403</v>
       </c>
       <c r="B21" t="s">
-        <v>393</v>
+        <v>404</v>
       </c>
       <c r="D21">
         <v>4090</v>
       </c>
       <c r="E21" t="s">
-        <v>393</v>
+        <v>404</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>394</v>
+        <v>405</v>
       </c>
       <c r="B22" t="s">
-        <v>395</v>
+        <v>406</v>
       </c>
       <c r="D22">
         <v>7010</v>
       </c>
       <c r="E22" t="s">
-        <v>395</v>
+        <v>406</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="B23" t="s">
-        <v>397</v>
+        <v>408</v>
       </c>
       <c r="D23" t="s">
-        <v>398</v>
+        <v>409</v>
       </c>
       <c r="E23" t="s">
-        <v>397</v>
+        <v>408</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" t="s">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="B24" t="s">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="D24" t="s">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="E24" t="s">
-        <v>400</v>
+        <v>411</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" t="s">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="B25" t="s">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="D25" t="s">
-        <v>401</v>
+        <v>412</v>
       </c>
       <c r="E25" t="s">
-        <v>402</v>
+        <v>413</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" t="s">
-        <v>346</v>
+        <v>357</v>
       </c>
       <c r="B26" t="s">
-        <v>346</v>
+        <v>357</v>
       </c>
       <c r="D26" t="s">
-        <v>403</v>
+        <v>414</v>
       </c>
       <c r="E26" t="s">
-        <v>404</v>
+        <v>415</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" t="s">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="B27" t="s">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="D27">
         <v>7020</v>
       </c>
       <c r="E27" t="s">
-        <v>405</v>
+        <v>416</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" t="s">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="B28" t="s">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="D28">
         <v>7020</v>
       </c>
       <c r="E28" t="s">
-        <v>406</v>
+        <v>417</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" t="s">
-        <v>359</v>
+        <v>370</v>
       </c>
       <c r="B29" t="s">
-        <v>359</v>
+        <v>370</v>
       </c>
       <c r="D29">
         <v>8030</v>
       </c>
       <c r="E29" t="s">
-        <v>407</v>
+        <v>418</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" t="s">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="B30" t="s">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="D30">
         <v>8040</v>
       </c>
       <c r="E30" t="s">
-        <v>408</v>
+        <v>419</v>
       </c>
     </row>
     <row r="31" ht="16.5" customHeight="1" spans="1:5">
       <c r="A31" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="B31" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="D31" t="s">
-        <v>409</v>
+        <v>420</v>
       </c>
       <c r="E31" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="32" ht="16.5" customHeight="1" spans="1:2">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="32" ht="16.5" customHeight="1" spans="1:5">
       <c r="A32" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="B32" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="33" ht="16.5" customHeight="1" spans="1:2">
+        <v>380</v>
+      </c>
+      <c r="D32" t="s">
+        <v>422</v>
+      </c>
+      <c r="E32" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="33" ht="16.5" customHeight="1" spans="1:5">
       <c r="A33" t="s">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c r="B33" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="34" ht="16.5" customHeight="1" spans="1:2">
+        <v>383</v>
+      </c>
+      <c r="D33" t="s">
+        <v>422</v>
+      </c>
+      <c r="E33" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="34" ht="16.5" customHeight="1" spans="1:5">
       <c r="A34" t="s">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="B34" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="35" ht="16.5" customHeight="1" spans="1:2">
+        <v>386</v>
+      </c>
+      <c r="D34" t="s">
+        <v>422</v>
+      </c>
+      <c r="E34" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="35" ht="16.5" customHeight="1" spans="1:5">
       <c r="A35" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="B35" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="36" ht="16.5" customHeight="1" spans="1:2">
+        <v>388</v>
+      </c>
+      <c r="D35" t="s">
+        <v>422</v>
+      </c>
+      <c r="E35" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="36" ht="16.5" customHeight="1" spans="1:5">
       <c r="A36" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="B36" t="s">
-        <v>379</v>
+        <v>390</v>
+      </c>
+      <c r="D36" t="s">
+        <v>422</v>
+      </c>
+      <c r="E36" t="s">
+        <v>426</v>
       </c>
     </row>
     <row r="37" ht="16.5" customHeight="1" spans="1:2">
       <c r="A37" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B37" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
     </row>
     <row r="38" ht="16.5" customHeight="1" spans="1:2">
       <c r="A38" t="s">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="B38" t="s">
-        <v>383</v>
+        <v>394</v>
       </c>
     </row>
     <row r="39" ht="16.5" customHeight="1" spans="1:2">
       <c r="A39" t="s">
-        <v>385</v>
+        <v>396</v>
       </c>
       <c r="B39" t="s">
-        <v>385</v>
+        <v>396</v>
       </c>
     </row>
     <row r="40" ht="16.5" customHeight="1" spans="1:2">
       <c r="A40" t="s">
-        <v>387</v>
+        <v>398</v>
       </c>
       <c r="B40" t="s">
-        <v>387</v>
+        <v>398</v>
       </c>
     </row>
     <row r="41" ht="16.5" customHeight="1" spans="1:2">
       <c r="A41" t="s">
-        <v>389</v>
+        <v>400</v>
       </c>
       <c r="B41" t="s">
-        <v>389</v>
+        <v>400</v>
       </c>
     </row>
     <row r="42" ht="16.5" customHeight="1" spans="1:2">
       <c r="A42" t="s">
-        <v>391</v>
+        <v>402</v>
       </c>
       <c r="B42" t="s">
-        <v>391</v>
+        <v>402</v>
       </c>
     </row>
     <row r="43" ht="16.5" customHeight="1" spans="1:2">
       <c r="A43" t="s">
-        <v>393</v>
+        <v>404</v>
       </c>
       <c r="B43" t="s">
-        <v>393</v>
+        <v>404</v>
       </c>
     </row>
     <row r="44" ht="16.5" customHeight="1" spans="1:2">
       <c r="A44" t="s">
-        <v>395</v>
+        <v>406</v>
       </c>
       <c r="B44" t="s">
-        <v>395</v>
+        <v>406</v>
       </c>
     </row>
     <row r="45" ht="16.5" customHeight="1" spans="1:2">
       <c r="A45" t="s">
-        <v>397</v>
+        <v>408</v>
       </c>
       <c r="B45" t="s">
-        <v>397</v>
+        <v>408</v>
       </c>
     </row>
     <row r="46" ht="16.5" customHeight="1" spans="1:2">
       <c r="A46" t="s">
+        <v>427</v>
+      </c>
+      <c r="B46" t="s">
         <v>411</v>
-      </c>
-      <c r="B46" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="47" ht="16.5" customHeight="1" spans="1:2">
       <c r="A47" t="s">
-        <v>412</v>
+        <v>428</v>
       </c>
       <c r="B47" t="s">
-        <v>402</v>
+        <v>413</v>
       </c>
     </row>
     <row r="48" ht="16.5" customHeight="1" spans="1:2">
       <c r="A48" t="s">
-        <v>413</v>
+        <v>429</v>
       </c>
       <c r="B48" t="s">
-        <v>404</v>
+        <v>415</v>
       </c>
     </row>
     <row r="49" ht="16.5" customHeight="1" spans="1:2">
       <c r="A49" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
       <c r="B49" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="50" ht="16.5" customHeight="1" spans="1:2">
       <c r="A50" t="s">
-        <v>416</v>
+        <v>431</v>
       </c>
       <c r="B50" t="s">
-        <v>406</v>
+        <v>417</v>
       </c>
     </row>
     <row r="51" ht="16.5" customHeight="1" spans="1:2">
       <c r="A51" t="s">
-        <v>400</v>
+        <v>411</v>
       </c>
       <c r="B51" t="s">
-        <v>400</v>
+        <v>411</v>
       </c>
     </row>
     <row r="52" ht="16.5" customHeight="1" spans="1:2">
       <c r="A52" t="s">
-        <v>402</v>
+        <v>413</v>
       </c>
       <c r="B52" t="s">
-        <v>402</v>
+        <v>413</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>404</v>
+        <v>415</v>
       </c>
       <c r="B53" t="s">
-        <v>404</v>
+        <v>415</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B54" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>406</v>
+        <v>417</v>
       </c>
       <c r="B55" t="s">
-        <v>406</v>
+        <v>417</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>417</v>
+        <v>432</v>
       </c>
       <c r="B56" t="s">
-        <v>375</v>
+        <v>386</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>418</v>
+        <v>433</v>
       </c>
       <c r="B57" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="B58" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>420</v>
+        <v>434</v>
       </c>
       <c r="B59" t="s">
-        <v>407</v>
+        <v>418</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>421</v>
+        <v>435</v>
       </c>
       <c r="B60" t="s">
-        <v>408</v>
+        <v>419</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>422</v>
+        <v>436</v>
       </c>
       <c r="B61" t="s">
-        <v>410</v>
+        <v>421</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
+        <v>437</v>
+      </c>
+      <c r="B62" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63" t="s">
+        <v>438</v>
+      </c>
+      <c r="B63" t="s">
         <v>423</v>
       </c>
-      <c r="B62" t="s">
-        <v>419</v>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64" t="s">
+        <v>430</v>
+      </c>
+      <c r="B64" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65" t="s">
+        <v>439</v>
+      </c>
+      <c r="B65" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66" t="s">
+        <v>425</v>
+      </c>
+      <c r="B66" t="s">
+        <v>425</v>
       </c>
     </row>
   </sheetData>
@@ -10940,25 +11133,25 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C40"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="2"/>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>424</v>
+        <v>440</v>
       </c>
       <c r="B1" t="s">
-        <v>425</v>
+        <v>441</v>
       </c>
       <c r="C1" t="s">
-        <v>426</v>
+        <v>442</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>427</v>
+        <v>443</v>
       </c>
       <c r="B2" t="s">
-        <v>427</v>
+        <v>443</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -10966,10 +11159,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c r="B3" t="s">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -10977,10 +11170,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="B4" t="s">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -10988,10 +11181,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="B5" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -10999,10 +11192,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="B6" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -11010,10 +11203,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B7" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -11021,10 +11214,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="B8" t="s">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -11032,10 +11225,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>385</v>
+        <v>396</v>
       </c>
       <c r="B9" t="s">
-        <v>385</v>
+        <v>396</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -11043,10 +11236,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="B10" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -11054,10 +11247,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>387</v>
+        <v>398</v>
       </c>
       <c r="B11" t="s">
-        <v>387</v>
+        <v>398</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -11065,10 +11258,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>389</v>
+        <v>400</v>
       </c>
       <c r="B12" t="s">
-        <v>389</v>
+        <v>400</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -11076,10 +11269,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>391</v>
+        <v>402</v>
       </c>
       <c r="B13" t="s">
-        <v>391</v>
+        <v>402</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -11087,10 +11280,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>393</v>
+        <v>404</v>
       </c>
       <c r="B14" t="s">
-        <v>393</v>
+        <v>404</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -11098,10 +11291,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="B15" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -11109,10 +11302,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="B16" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -11120,10 +11313,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="B17" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -11131,10 +11324,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="B18" t="s">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -11142,10 +11335,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>430</v>
+        <v>444</v>
       </c>
       <c r="B19" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -11153,10 +11346,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>346</v>
+        <v>357</v>
       </c>
       <c r="B20" t="s">
-        <v>346</v>
+        <v>357</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -11164,10 +11357,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>431</v>
+        <v>445</v>
       </c>
       <c r="B21" t="s">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -11175,10 +11368,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="B22" t="s">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -11186,10 +11379,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>395</v>
+        <v>406</v>
       </c>
       <c r="B23" t="s">
-        <v>395</v>
+        <v>406</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -11197,10 +11390,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>432</v>
+        <v>446</v>
       </c>
       <c r="B24" t="s">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -11208,10 +11401,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>433</v>
+        <v>447</v>
       </c>
       <c r="B25" t="s">
-        <v>359</v>
+        <v>370</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -11219,10 +11412,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>400</v>
+        <v>411</v>
       </c>
       <c r="B26" t="s">
-        <v>400</v>
+        <v>411</v>
       </c>
       <c r="C26">
         <v>0</v>
@@ -11230,10 +11423,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>404</v>
+        <v>415</v>
       </c>
       <c r="B27" t="s">
-        <v>404</v>
+        <v>415</v>
       </c>
       <c r="C27">
         <v>0</v>
@@ -11241,10 +11434,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>434</v>
+        <v>448</v>
       </c>
       <c r="B28" t="s">
-        <v>402</v>
+        <v>413</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -11252,10 +11445,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>405</v>
+        <v>416</v>
       </c>
       <c r="B29" t="s">
-        <v>405</v>
+        <v>416</v>
       </c>
       <c r="C29">
         <v>0</v>
@@ -11263,10 +11456,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>406</v>
+        <v>417</v>
       </c>
       <c r="B30" t="s">
-        <v>406</v>
+        <v>417</v>
       </c>
       <c r="C30">
         <v>0</v>
@@ -11274,10 +11467,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>435</v>
+        <v>449</v>
       </c>
       <c r="B31" t="s">
-        <v>407</v>
+        <v>418</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -11285,10 +11478,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>436</v>
+        <v>450</v>
       </c>
       <c r="B32" t="s">
-        <v>408</v>
+        <v>419</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -11296,10 +11489,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>437</v>
+        <v>451</v>
       </c>
       <c r="B33" t="s">
-        <v>410</v>
+        <v>421</v>
       </c>
       <c r="C33">
         <v>1</v>
@@ -11307,10 +11500,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>397</v>
+        <v>408</v>
       </c>
       <c r="B34" t="s">
-        <v>397</v>
+        <v>408</v>
       </c>
       <c r="C34">
         <v>0</v>
@@ -11318,10 +11511,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>438</v>
+        <v>452</v>
       </c>
       <c r="B35" t="s">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="C35">
         <v>0</v>
@@ -11329,10 +11522,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>439</v>
+        <v>453</v>
       </c>
       <c r="B36" t="s">
-        <v>346</v>
+        <v>357</v>
       </c>
       <c r="C36">
         <v>0</v>
@@ -11340,10 +11533,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>440</v>
+        <v>424</v>
       </c>
       <c r="B37" t="s">
-        <v>427</v>
+        <v>443</v>
       </c>
       <c r="C37">
         <v>0</v>
@@ -11351,10 +11544,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="B38" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="C38">
         <v>0</v>
@@ -11362,10 +11555,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>441</v>
+        <v>454</v>
       </c>
       <c r="B39" t="s">
-        <v>441</v>
+        <v>454</v>
       </c>
       <c r="C39">
         <v>0</v>
@@ -11373,10 +11566,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>423</v>
+        <v>455</v>
       </c>
       <c r="B40" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="C40">
         <v>0</v>
@@ -11393,9 +11586,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:K5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="4"/>
   <cols>
-    <col min="7" max="7" width="23.3362831858407" customWidth="1"/>
+    <col min="7" max="7" width="23.3363636363636" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -11409,19 +11602,19 @@
         <v>32</v>
       </c>
       <c r="D1" t="s">
-        <v>442</v>
+        <v>456</v>
       </c>
       <c r="E1" t="s">
-        <v>443</v>
+        <v>457</v>
       </c>
       <c r="F1" t="s">
-        <v>444</v>
+        <v>458</v>
       </c>
       <c r="G1" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="H1" t="s">
-        <v>446</v>
+        <v>460</v>
       </c>
       <c r="I1" t="s">
         <v>2</v>
@@ -11429,21 +11622,21 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="3" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>447</v>
+        <v>461</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>448</v>
+        <v>462</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>449</v>
+        <v>463</v>
       </c>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
       <c r="G2" s="3" t="s">
-        <v>450</v>
+        <v>464</v>
       </c>
       <c r="H2" s="3">
         <v>11</v>
@@ -11465,76 +11658,76 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="4" outlineLevelCol="5"/>
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>29</v>
       </c>
       <c r="B1" t="s">
-        <v>451</v>
+        <v>465</v>
       </c>
       <c r="C1" t="s">
-        <v>452</v>
+        <v>466</v>
       </c>
       <c r="D1" t="s">
         <v>2</v>
       </c>
       <c r="E1" t="s">
-        <v>453</v>
+        <v>467</v>
       </c>
       <c r="F1" t="s">
-        <v>454</v>
+        <v>468</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>455</v>
+        <v>469</v>
       </c>
       <c r="B2" t="s">
-        <v>456</v>
+        <v>470</v>
       </c>
       <c r="C2" t="s">
-        <v>456</v>
+        <v>470</v>
       </c>
       <c r="D2" t="s">
-        <v>457</v>
+        <v>471</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>455</v>
+        <v>469</v>
       </c>
       <c r="B3" t="s">
-        <v>458</v>
+        <v>472</v>
       </c>
       <c r="C3" t="s">
-        <v>458</v>
+        <v>472</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>455</v>
+        <v>469</v>
       </c>
       <c r="B4" t="s">
-        <v>459</v>
+        <v>473</v>
       </c>
       <c r="C4" t="s">
-        <v>459</v>
+        <v>473</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>455</v>
+        <v>469</v>
       </c>
       <c r="B5" t="s">
-        <v>460</v>
+        <v>474</v>
       </c>
       <c r="C5" t="s">
-        <v>460</v>
+        <v>474</v>
       </c>
       <c r="D5" t="s">
-        <v>461</v>
+        <v>475</v>
       </c>
     </row>
   </sheetData>
